--- a/02_加值成品/八下/八下3-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下3-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下3-2 酸與鹼　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下3-2 酸與鹼　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>酸在水中解離出？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>氫氧根OH⁻</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>藍</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>廣用試紙</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>氫離子H⁺</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>酸性來源</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>鹼在水中解離出？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>H⁺</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>酸味</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>氫氧根OH⁻</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>鹼性來源</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>酸使藍色石蕊變？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>OH⁻</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>紅</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>氫氧根OH⁻</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>酸紅</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>鹼使紅色石蕊變？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>藍</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>碳酸鈣</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>氫離子H⁺</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>H⁺</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>鹼藍</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>酸嚐起來是什麼味？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>酸味</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>藍</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>氫氣</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>該液為鹼性</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>特徵</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>鹼摸起來有什麼感覺？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>紅</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>氫氧根OH⁻</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>滑膩</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>藍</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>特徵</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>酸與活性金屬反應產生？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>氫氣</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>氫離子H⁺</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>該液為鹼性</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>冒泡</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>看pH常用什麼？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>廣用試紙</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>氫氣</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>滑膩</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>指示</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>酸使石蕊試紙變什麼色？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>酸味</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>H⁺</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>碳酸鈣</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>紅色</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>酸紅</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>常見的鹼舉一例？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>用石蕊或廣用試紙測</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>氫氧化鈉/氨水</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>冒氫氣泡、鎂溶解</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>CO₂,通入石灰水變混濁</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>鹼</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下3-2 酸與鹼　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下3-2 酸與鹼　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>鎂帶放入稀鹽酸產生？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>氫離子H⁺</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>氫氣</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>碳酸鈣</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>H⁺</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>活性金屬</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>稀鹽酸與大理石反應產生？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>酸味</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>二氧化碳</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>氫氧根OH⁻</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>紅</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>CO₂</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>銅放入稀鹽酸會反應嗎？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>該液為鹼性</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>酸味</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>紅</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>不會</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>活性小</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>酚酞在鹼性中變？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>酸味</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>紅</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>碳酸鈣</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>紅色</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>指示劑</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>酸性溶液pH如何？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>氫離子H⁺</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>紅色</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>小於7</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>該液為鹼性</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>偏酸</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>鹼性溶液pH如何？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>大於7</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>酸味</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>前者產氫、後者產CO₂</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>藍</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>偏鹼</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>大理石主成分是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>氫氣</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>碳酸鈣</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>紅</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>酸味</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>CaCO₃</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>酸與金屬反應除氫氣還生成？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>滑膩</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>氫氣</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>H⁺</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>鹽</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>產物</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>酸與鎂帶反應冒出的氣體是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>滑膩</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>H⁺</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>氫氣</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>氫氧根OH⁻</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>產氫</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>酸與大理石反應冒出的氣體是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>二氧化碳</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>OH⁻</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>H⁺</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>滑膩</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>產CO₂</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下3-2 酸與鹼　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下3-2 酸與鹼　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>如何用一支廣用試紙分辨三種未知液酸鹼？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>沾取比對顏色對照pH</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>氫氧化鈉/氨水</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>具腐蝕性傷害組織</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>前者產氫、後者產CO₂</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>檢測</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>鎂帶與稀硫酸反應的觀察現象？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>用石蕊或廣用試紙測</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>具腐蝕性傷害組織</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>冒氫氣泡、鎂溶解</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>沾取比對顏色對照pH</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>現象</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>稀鹽酸滴在大理石上冒泡是什麼氣體?如何驗證？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>氫氧化鈉/氨水</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>具腐蝕性傷害組織</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>CO₂,通入石灰水變混濁</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>沾取比對顏色對照pH</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>驗證</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>為何強酸強鹼不可用口嚐？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>含酸解離出H⁺</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>前者產氫、後者產CO₂</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>具腐蝕性傷害組織</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>CO₂,通入石灰水變混濁</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>安全</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>酸的共同性質來自哪種離子？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>H⁺</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>藍</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>廣用試紙</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>氫氧根OH⁻</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>本質</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>比較酸與活性金屬、與大理石反應產物差異？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>冒氫氣泡、鎂溶解</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>氫氧化鈉/氨水</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>具腐蝕性傷害組織</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>前者產氫、後者產CO₂</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>鹼的滑膩感與哪種離子有關？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>OH⁻</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>紅色</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>藍</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>滑膩</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>鹼性</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>無色酚酞滴入某液變紅表示？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>氫氣</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>該液為鹼性</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>酸味</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>判斷</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何檸檬吃起來酸？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>含酸解離出H⁺</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>沾取比對顏色對照pH</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>用石蕊或廣用試紙測</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>冒氫氣泡、鎂溶解</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>酸</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>如何區分兩瓶無色的酸與鹼？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>冒氫氣泡、鎂溶解</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>沾取比對顏色對照pH</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>用石蕊或廣用試紙測</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>前者產氫、後者產CO₂</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>檢測</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下3-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下3-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>酸性來源</t>
+          <t>酸性來源：酸溶在水裡會拆出帶正電的氫離子，正是這個離子讓溶液帶有酸的性質</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>鹼性來源</t>
+          <t>鹼性來源：鹼溶在水裡會拆出帶負電的氫氧根離子，正是這個離子讓溶液帶有鹼的性質</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>酸紅</t>
+          <t>酸紅：這是酸性溶液的一個判斷方法，藍色石蕊試紙碰到酸會變成紅色</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>鹼藍</t>
+          <t>鹼藍：這是鹼性溶液的一個判斷方法，紅色石蕊試紙碰到鹼會變成藍色</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>特徵</t>
+          <t>特徵：像檸檬、醋這類含酸的食物，吃起來會有酸酸的味道，這是酸的特徵之一</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>特徵</t>
+          <t>特徵：像肥皂水這類鹼性液體，摸起來會有滑滑膩膩的觸感，這是鹼的特徵之一</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>冒泡</t>
+          <t>冒泡：酸和活性夠大的金屬反應時，會把金屬中的氫離子變成氫氣冒出來，看起來像冒泡</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>指示</t>
+          <t>指示：把廣用試紙沾一下溶液，再對照顏色卡就能大概知道溶液的pH值是多少</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>酸紅</t>
+          <t>酸紅：酸性溶液會使藍色石蕊試紙變成紅色，這是判斷溶液是否為酸性的常用方法</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>鹼</t>
+          <t>鹼：常見的鹼類物質例如氫氧化鈉、氨水等，都具有鹼性</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>活性金屬</t>
+          <t>活性金屬：鎂的活性夠大，能和鹽酸反應把氫離子變成氫氣釋放出來，形成許多氣泡</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>CO₂</t>
+          <t>CO₂：大理石的主要成分是碳酸鈣，遇到鹽酸會反應生成二氧化碳氣體冒出來</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>活性小</t>
+          <t>活性小：銅的活性太小，沒辦法把鹽酸裡的氫離子換出來，所以放進去不會有反應</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>指示劑</t>
+          <t>指示劑：無色的酚酞溶液滴入鹼性溶液後會變成粉紅色，是常用來判斷鹼性的指示劑</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>偏酸</t>
+          <t>偏酸：pH值是用來表示酸鹼程度的數字，只要小於7就代表這杯溶液是偏酸性的</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>偏鹼</t>
+          <t>偏鹼：pH值是用來表示酸鹼程度的數字，只要大於7就代表這杯溶液是偏鹼性的</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>CaCO₃</t>
+          <t>CaCO₃：大理石這種石頭主要是由碳酸鈣這種化合物組成的，會和酸產生反應</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>產物</t>
+          <t>產物：酸和活性金屬反應時，除了放出氫氣，金屬還會和酸根結合形成另一種產物叫做鹽</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>產氫</t>
+          <t>產氫：活潑金屬(如鎂)和酸反應時會置換出氫氣，這也是實驗室常見的產氫方式</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>產CO₂</t>
+          <t>產CO₂：大理石主要成分是碳酸鈣，和酸反應會生成二氧化碳氣體，實驗中可以看到冒泡現象</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>檢測</t>
+          <t>檢測：分別用試紙沾一下三種液體，再把顯示出的顏色拿去對照色卡，就能判斷各自的酸鹼程度</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>現象</t>
+          <t>現象：鎂帶放進稀硫酸後會看到表面冒出許多小氣泡（氫氣），同時鎂帶本身也會逐漸變小溶解掉</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>驗證</t>
+          <t>驗證：冒出的氣體是二氧化碳，只要把這氣體通入澄清石灰水，石灰水會變得混濁就能證實</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>安全</t>
+          <t>安全：濃度很高的強酸強鹼會腐蝕破壞皮膚和口腔黏膜組織，非常危險，絕對不能用嘴巴嚐試</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>本質</t>
+          <t>本質：不管是哪一種酸，只要溶於水都會產生氫離子，各種酸表現出的共同性質都是這個離子造成的</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>對比：酸和活性金屬反應會放出氫氣，而酸和大理石（碳酸鈣）反應則是放出二氧化碳氣體，產物不同</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>鹼性</t>
+          <t>鹼性：鹼溶液中的氫氧根離子會和皮膚表面的油脂產生作用，摸起來才會有滑滑膩膩的感覺</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>判斷</t>
+          <t>判斷：酚酞是遇到鹼性溶液才會由無色轉變成粉紅色的指示劑，所以變紅就代表這杯液體是鹼性的</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>酸</t>
+          <t>酸：檸檬含有檸檬酸等酸性物質，溶於水（如口水）中會解離出氫離子(H⁺)，正是這些氫離子刺激味覺產生酸的感覺</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>檢測</t>
+          <t>檢測：可以用石蕊試紙或廣用試紙分別測試兩瓶無色液體，觀察試紙變色情形（酸使石蕊變紅、鹼使石蕊變藍），藉此判斷哪一瓶是酸、哪一瓶是鹼</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下3-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下3-2_三種難度測驗卷.xlsx
@@ -563,17 +563,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>氫氧根OH⁻</t>
+          <t>廣用試紙</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>藍</t>
+          <t>OH⁻</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>廣用試紙</t>
+          <t>酸味</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>H⁺</t>
+          <t>氫氣</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>二氧化碳</t>
+          <t>碳酸鈣</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>OH⁻</t>
+          <t>二氧化碳</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>二氧化碳</t>
+          <t>不會</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>氫氧根OH⁻</t>
+          <t>廣用試紙</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>H⁺</t>
+          <t>二氧化碳</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>碳酸鈣</t>
+          <t>氫氣</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1159,17 +1159,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>酸味</t>
+          <t>氫氧根OH⁻</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>紅</t>
+          <t>H⁺</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>碳酸鈣</t>
+          <t>該液為鹼性</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>氫離子H⁺</t>
+          <t>碳酸鈣</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>紅色</t>
+          <t>酸味</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>該液為鹼性</t>
+          <t>OH⁻</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1244,17 +1244,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>酸味</t>
+          <t>OH⁻</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>前者產氫、後者產CO₂</t>
+          <t>滑膩</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>藍</t>
+          <t>小於7</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1680,17 +1680,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>藍</t>
+          <t>廣用試紙</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>廣用試紙</t>
+          <t>酸味</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>氫氧根OH⁻</t>
+          <t>滑膩</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>紅色</t>
+          <t>酸味</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>藍</t>
+          <t>H⁺</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>滑膩</t>
+          <t>氫離子H⁺</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
